--- a/output/pdf_financials_xlsx/UDOC.xlsx
+++ b/output/pdf_financials_xlsx/UDOC.xlsx
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.935887</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.299759</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.212208</v>
       </c>
     </row>
     <row r="93">
@@ -3349,7 +3349,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -3787,7 +3791,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.935887</v>
       </c>

--- a/output/pdf_financials_xlsx/UDOC.xlsx
+++ b/output/pdf_financials_xlsx/UDOC.xlsx
@@ -618,10 +618,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001402</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000318</v>
       </c>
     </row>
     <row r="13">
@@ -870,10 +870,10 @@
         <v>-1.357064</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.259842</v>
+        <v>-2.261244</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-6.063481</v>
+        <v>-6.063799</v>
       </c>
     </row>
     <row r="28">
@@ -902,10 +902,10 @@
         <v>-1.29284</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.191581</v>
+        <v>-2.192983</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.025911</v>
+        <v>-6.026229</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.051323</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.398885</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.253219</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.051323</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.398885</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.253219</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.052207</v>
+        <v>0.000884</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.419792</v>
+        <v>0.020907</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.89847</v>
+        <v>0.645251</v>
       </c>
     </row>
     <row r="49">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">

--- a/output/pdf_financials_xlsx/UDOC.xlsx
+++ b/output/pdf_financials_xlsx/UDOC.xlsx
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.292805</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.637943</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.263783</v>
       </c>
     </row>
     <row r="68">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.062768</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.25243</v>
       </c>
     </row>
     <row r="117">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.062768</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.755589</v>
+        <v>-0.818357</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.55992</v>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4930,7 +4930,11 @@
           <t>Purchase of equipment $</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
         <v>-0.062768</v>
       </c>
